--- a/ProjectProgress/表格/分类进展/游戏设计.xlsx
+++ b/ProjectProgress/表格/分类进展/游戏设计.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="游戏设计" sheetId="1" r:id="R300f17ac90a04f3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="游戏设计" sheetId="1" r:id="R35dc4bb4c71d44b1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -192,8 +192,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress9" displayName="CategoryProgress9" ref="A7:H14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A7:H14"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress9" displayName="CategoryProgress9" ref="A7:H15" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A7:H15"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="编号"/>
     <x:tableColumn id="2" name="事项"/>
@@ -427,7 +427,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-09-30 17:14:21（北京时间）</x:v>
+        <x:v>更新于 2026-10-04 09:15:53（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -464,22 +464,22 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="B5" s="5" t="n">
-        <x:f>COUNTIF(C8:C14,A5)</x:f>
-        <x:v>4</x:v>
+        <x:f>COUNTIF(C8:C15,A5)</x:f>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1" t="str">
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="E5" s="5" t="n">
-        <x:f>COUNTIF(C8:C14,D5)</x:f>
+        <x:f>COUNTIF(C8:C15,D5)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="1" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="G5" s="5" t="n">
-        <x:f>COUNTIF(C8:C14,F5)</x:f>
+        <x:f>COUNTIF(C8:C15,F5)</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="H5" s="1"/>
@@ -651,16 +651,16 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D13" s="7" t="str">
-        <x:v>当前探索操作已明确：播放后自动进入第一人称，WASD 移动、鼠标观察、空格跳跃，Esc 退出试玩；角色站在校园地面且身体不遮挡视线。</x:v>
+        <x:v>原第一人称校园探索阶段已交付。10月4日为满足唯一White要求，scene玩家改为SpectatorPawn无人物观察入口，WASD、鼠标及Q/E升降浏览已运行确认。</x:v>
       </x:c>
       <x:c r="E13" s="7" t="str">
-        <x:v>延续当前操作规则，后续交互设计与已用 E 键规则保持一致。</x:v>
+        <x:v>当前规则见CA-054；整体游戏目标仍按CA-018.03待确认，不从入口变化自行新增功能。</x:v>
       </x:c>
       <x:c r="F13" s="14" t="n">
-        <x:v>46290</x:v>
+        <x:v>46299</x:v>
       </x:c>
       <x:c r="G13" s="7" t="str">
-        <x:v>第一人称角色聊天操作说明与实测</x:v>
+        <x:v>用户人数要求与观察玩法入口</x:v>
       </x:c>
       <x:c r="H13" s="16" t="str"/>
     </x:row>
@@ -688,45 +688,69 @@
       </x:c>
       <x:c r="H14" s="16" t="str"/>
     </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="1"/>
-      <x:c r="B15" s="1"/>
-      <x:c r="C15" s="1"/>
-      <x:c r="D15" s="1"/>
-      <x:c r="E15" s="1"/>
-      <x:c r="F15" s="1"/>
-      <x:c r="G15" s="1"/>
-      <x:c r="H15" s="1"/>
-    </x:row>
-    <x:row r="16" ht="34" customHeight="1">
-      <x:c r="A16" s="3" t="str">
+    <x:row r="15" ht="92" customHeight="1">
+      <x:c r="A15" s="7" t="str">
+        <x:v>CA-054</x:v>
+      </x:c>
+      <x:c r="B15" s="7" t="str">
+        <x:v>scene无人物模型观察摄像机入口</x:v>
+      </x:c>
+      <x:c r="C15" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D15" s="7" t="str">
+        <x:v>按仅保留一名White的最新要求，scene使用BP_CampusObservationGameMode和原生SpectatorPawn，玩家无人物网格，WASD/鼠标浏览、Q/E升降。</x:v>
+      </x:c>
+      <x:c r="E15" s="7" t="str">
+        <x:v>当前玩法入口取代默认第一人称人物；旧发布包为早期版本见CA-046.02。</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="n">
+        <x:v>46299</x:v>
+      </x:c>
+      <x:c r="G15" s="7" t="str">
+        <x:v>单White保存与观察模式说明</x:v>
+      </x:c>
+      <x:c r="H15" s="16" t="str"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="1"/>
+      <x:c r="B16" s="1"/>
+      <x:c r="C16" s="1"/>
+      <x:c r="D16" s="1"/>
+      <x:c r="E16" s="1"/>
+      <x:c r="F16" s="1"/>
+      <x:c r="G16" s="1"/>
+      <x:c r="H16" s="1"/>
+    </x:row>
+    <x:row r="17" ht="34" customHeight="1">
+      <x:c r="A17" s="3" t="str">
         <x:v>记录范围</x:v>
       </x:c>
-      <x:c r="B16" s="21" t="str">
+      <x:c r="B17" s="21" t="str">
         <x:v>状态以项目聊天及验收记录为依据，每条仅计入一个分类。缺少最终验收或需要决定的事项标为待确认。</x:v>
       </x:c>
-      <x:c r="C16" s="21"/>
-      <x:c r="D16" s="21"/>
-      <x:c r="E16" s="21"/>
-      <x:c r="F16" s="21"/>
-      <x:c r="G16" s="21"/>
-      <x:c r="H16" s="21"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="1"/>
-      <x:c r="B17" s="1"/>
-      <x:c r="C17" s="1"/>
-      <x:c r="D17" s="1"/>
-      <x:c r="E17" s="1"/>
-      <x:c r="F17" s="1"/>
-      <x:c r="G17" s="1"/>
-      <x:c r="H17" s="1"/>
+      <x:c r="C17" s="21"/>
+      <x:c r="D17" s="21"/>
+      <x:c r="E17" s="21"/>
+      <x:c r="F17" s="21"/>
+      <x:c r="G17" s="21"/>
+      <x:c r="H17" s="21"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="1"/>
+      <x:c r="B18" s="1"/>
+      <x:c r="C18" s="1"/>
+      <x:c r="D18" s="1"/>
+      <x:c r="E18" s="1"/>
+      <x:c r="F18" s="1"/>
+      <x:c r="G18" s="1"/>
+      <x:c r="H18" s="1"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="B16:H16"/>
+    <x:mergeCell ref="B17:H17"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="C8:C14">
+  <x:conditionalFormatting sqref="C8:C15">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>$C8="已完成"</x:formula>
     </x:cfRule>
@@ -738,13 +762,13 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="C8:C14">
+    <x:dataValidation type="list" sqref="C8:C15">
       <x:formula1>"已完成,进行中,待确认"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe27588617ed429c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R944003e025ca4d51"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/ProjectProgress/表格/分类进展/游戏设计.xlsx
+++ b/ProjectProgress/表格/分类进展/游戏设计.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="游戏设计" sheetId="1" r:id="R35dc4bb4c71d44b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="游戏设计" sheetId="1" r:id="Rc3dd4abf287d4e56"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -192,8 +192,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress9" displayName="CategoryProgress9" ref="A7:H15" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A7:H15"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress9" displayName="CategoryProgress9" ref="A7:H16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A7:H16"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="编号"/>
     <x:tableColumn id="2" name="事项"/>
@@ -427,7 +427,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-10-04 09:15:53（北京时间）</x:v>
+        <x:v>更新于 2026-10-05 09:12:49（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -464,22 +464,22 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="B5" s="5" t="n">
-        <x:f>COUNTIF(C8:C15,A5)</x:f>
-        <x:v>5</x:v>
+        <x:f>COUNTIF(C8:C16,A5)</x:f>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1" t="str">
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="E5" s="5" t="n">
-        <x:f>COUNTIF(C8:C15,D5)</x:f>
+        <x:f>COUNTIF(C8:C16,D5)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="1" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="G5" s="5" t="n">
-        <x:f>COUNTIF(C8:C15,F5)</x:f>
+        <x:f>COUNTIF(C8:C16,F5)</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="H5" s="1"/>
@@ -651,16 +651,16 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D13" s="7" t="str">
-        <x:v>原第一人称校园探索阶段已交付。10月4日为满足唯一White要求，scene玩家改为SpectatorPawn无人物观察入口，WASD、鼠标及Q/E升降浏览已运行确认。</x:v>
+        <x:v>当前默认第一人称校园探索，WASD移动、原生视角控制、空格跳跃，15项运行检查通过。早先观察模式为10月4日人数精简时的阶段配置，后被用户明确默认第一人称要求取代。</x:v>
       </x:c>
       <x:c r="E13" s="7" t="str">
-        <x:v>当前规则见CA-054；整体游戏目标仍按CA-018.03待确认，不从入口变化自行新增功能。</x:v>
+        <x:v>整体游戏目标仍见CA-018.03；不从新入口自行扩展功能。</x:v>
       </x:c>
       <x:c r="F13" s="14" t="n">
         <x:v>46299</x:v>
       </x:c>
       <x:c r="G13" s="7" t="str">
-        <x:v>用户人数要求与观察玩法入口</x:v>
+        <x:v>用户默认第一人称选择与新版交付</x:v>
       </x:c>
       <x:c r="H13" s="16" t="str"/>
     </x:row>
@@ -693,64 +693,88 @@
         <x:v>CA-054</x:v>
       </x:c>
       <x:c r="B15" s="7" t="str">
-        <x:v>scene无人物模型观察摄像机入口</x:v>
+        <x:v>scene无人物模型观察入口阶段交付</x:v>
       </x:c>
       <x:c r="C15" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D15" s="7" t="str">
-        <x:v>按仅保留一名White的最新要求，scene使用BP_CampusObservationGameMode和原生SpectatorPawn，玩家无人物网格，WASD/鼠标浏览、Q/E升降。</x:v>
+        <x:v>10月4日人数精简阶段的SpectatorPawn观察入口曾保存并验收。后续用户明确要求启动默认第一人称，已恢复人物入口；该记录保留为已完成历史阶段。</x:v>
       </x:c>
       <x:c r="E15" s="7" t="str">
-        <x:v>当前玩法入口取代默认第一人称人物；旧发布包为早期版本见CA-046.02。</x:v>
+        <x:v>当前入口见CA-018和CA-018.02，不再按观察摄像机描述当前运行。</x:v>
       </x:c>
       <x:c r="F15" s="14" t="n">
         <x:v>46299</x:v>
       </x:c>
       <x:c r="G15" s="7" t="str">
-        <x:v>单White保存与观察模式说明</x:v>
+        <x:v>观察阶段基线与后续用户入口纠正</x:v>
       </x:c>
       <x:c r="H15" s="16" t="str"/>
     </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="1"/>
-      <x:c r="B16" s="1"/>
-      <x:c r="C16" s="1"/>
-      <x:c r="D16" s="1"/>
-      <x:c r="E16" s="1"/>
-      <x:c r="F16" s="1"/>
-      <x:c r="G16" s="1"/>
-      <x:c r="H16" s="1"/>
-    </x:row>
-    <x:row r="17" ht="34" customHeight="1">
-      <x:c r="A17" s="3" t="str">
+    <x:row r="16" ht="75" customHeight="1">
+      <x:c r="A16" s="7" t="str">
+        <x:v>CA-058.04</x:v>
+      </x:c>
+      <x:c r="B16" s="7" t="str">
+        <x:v>演讲区域遮阳设施概念图交付</x:v>
+      </x:c>
+      <x:c r="C16" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D16" s="7" t="str">
+        <x:v>本项目图片生成聊天已交付浅米白弧顶方案，保留演讲台视线、台阶与旗帜空间，后续独立棚模型另见CA-058。</x:v>
+      </x:c>
+      <x:c r="E16" s="7" t="str">
+        <x:v>图片设计交付与UE落地分别记录。</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="n">
+        <x:v>46299</x:v>
+      </x:c>
+      <x:c r="G16" s="7" t="str">
+        <x:v>项目关联图片聊天最终交付</x:v>
+      </x:c>
+      <x:c r="H16" s="16" t="str"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="1"/>
+      <x:c r="B17" s="1"/>
+      <x:c r="C17" s="1"/>
+      <x:c r="D17" s="1"/>
+      <x:c r="E17" s="1"/>
+      <x:c r="F17" s="1"/>
+      <x:c r="G17" s="1"/>
+      <x:c r="H17" s="1"/>
+    </x:row>
+    <x:row r="18" ht="34" customHeight="1">
+      <x:c r="A18" s="3" t="str">
         <x:v>记录范围</x:v>
       </x:c>
-      <x:c r="B17" s="21" t="str">
+      <x:c r="B18" s="21" t="str">
         <x:v>状态以项目聊天及验收记录为依据，每条仅计入一个分类。缺少最终验收或需要决定的事项标为待确认。</x:v>
       </x:c>
-      <x:c r="C17" s="21"/>
-      <x:c r="D17" s="21"/>
-      <x:c r="E17" s="21"/>
-      <x:c r="F17" s="21"/>
-      <x:c r="G17" s="21"/>
-      <x:c r="H17" s="21"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="1"/>
-      <x:c r="B18" s="1"/>
-      <x:c r="C18" s="1"/>
-      <x:c r="D18" s="1"/>
-      <x:c r="E18" s="1"/>
-      <x:c r="F18" s="1"/>
-      <x:c r="G18" s="1"/>
-      <x:c r="H18" s="1"/>
+      <x:c r="C18" s="21"/>
+      <x:c r="D18" s="21"/>
+      <x:c r="E18" s="21"/>
+      <x:c r="F18" s="21"/>
+      <x:c r="G18" s="21"/>
+      <x:c r="H18" s="21"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="1"/>
+      <x:c r="B19" s="1"/>
+      <x:c r="C19" s="1"/>
+      <x:c r="D19" s="1"/>
+      <x:c r="E19" s="1"/>
+      <x:c r="F19" s="1"/>
+      <x:c r="G19" s="1"/>
+      <x:c r="H19" s="1"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="B17:H17"/>
+    <x:mergeCell ref="B18:H18"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="C8:C15">
+  <x:conditionalFormatting sqref="C8:C16">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>$C8="已完成"</x:formula>
     </x:cfRule>
@@ -762,13 +786,13 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="C8:C15">
+    <x:dataValidation type="list" sqref="C8:C16">
       <x:formula1>"已完成,进行中,待确认"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R944003e025ca4d51"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00fce817b1564272"/>
   </x:tableParts>
 </x:worksheet>
 </file>